--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487023_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487023_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.0833</v>
+        <v>6.9434</v>
       </c>
       <c r="E2" t="n">
-        <v>3.2923</v>
+        <v>3.5674</v>
       </c>
       <c r="F2" t="n">
-        <v>3.791</v>
+        <v>3.376</v>
       </c>
       <c r="G2" t="n">
         <v>5.7636</v>
@@ -610,13 +610,13 @@
         <v>1.8481</v>
       </c>
       <c r="S2" t="n">
-        <v>0.4983</v>
+        <v>0.3584</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.4147</v>
+        <v>-0.1397</v>
       </c>
       <c r="U2" t="n">
-        <v>0.9131</v>
+        <v>0.4981</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. MONTILLA DIAZ</t>
+          <t>C. HURTADO CERVANTES</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.5094</v>
+        <v>5.5159</v>
       </c>
       <c r="E3" t="n">
-        <v>3.4741</v>
+        <v>2.9228</v>
       </c>
       <c r="F3" t="n">
-        <v>2.0352</v>
+        <v>2.5931</v>
       </c>
       <c r="G3" t="n">
-        <v>1.9714</v>
+        <v>2.5344</v>
       </c>
       <c r="H3" t="n">
-        <v>2.1477</v>
+        <v>-1.5992</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1763</v>
+        <v>4.1336</v>
       </c>
       <c r="J3" t="n">
-        <v>2.1102</v>
+        <v>2.4808</v>
       </c>
       <c r="K3" t="n">
-        <v>2.7286</v>
+        <v>-0.7684</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.6183999999999999</v>
+        <v>3.2492</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.1388</v>
+        <v>0.0535</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.581</v>
+        <v>-0.8308</v>
       </c>
       <c r="O3" t="n">
-        <v>0.4422</v>
+        <v>0.8843</v>
       </c>
       <c r="P3" t="n">
-        <v>0.8214</v>
+        <v>1.4374</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.0267</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.8481</v>
+        <v>1.4374</v>
       </c>
       <c r="S3" t="n">
-        <v>2.1273</v>
+        <v>0.2567</v>
       </c>
       <c r="T3" t="n">
-        <v>1.8013</v>
+        <v>-0.3876</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3259</v>
+        <v>0.6443</v>
       </c>
       <c r="V3" t="n">
-        <v>0.5893</v>
+        <v>1.2875</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5893</v>
+        <v>0.8295</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>0.4579</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>C. HURTADO CERVANTES</t>
+          <t>K. GREELEY</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.2944</v>
+        <v>5.3474</v>
       </c>
       <c r="E4" t="n">
-        <v>3.0274</v>
+        <v>2.3114</v>
       </c>
       <c r="F4" t="n">
-        <v>2.2671</v>
+        <v>3.0359</v>
       </c>
       <c r="G4" t="n">
-        <v>2.5344</v>
+        <v>5.8064</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.5992</v>
+        <v>1.2886</v>
       </c>
       <c r="I4" t="n">
-        <v>4.1336</v>
+        <v>4.5179</v>
       </c>
       <c r="J4" t="n">
-        <v>2.4808</v>
+        <v>4.582</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.7684</v>
+        <v>1.2274</v>
       </c>
       <c r="L4" t="n">
-        <v>3.2492</v>
+        <v>3.3546</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0535</v>
+        <v>1.2245</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.8308</v>
+        <v>0.0612</v>
       </c>
       <c r="O4" t="n">
-        <v>0.8843</v>
+        <v>1.1633</v>
       </c>
       <c r="P4" t="n">
-        <v>1.4374</v>
+        <v>-0.4107</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-2.0534</v>
       </c>
       <c r="R4" t="n">
-        <v>1.4374</v>
+        <v>1.6427</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0352</v>
+        <v>-0.0484</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.283</v>
+        <v>-0.2171</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3182</v>
+        <v>0.1687</v>
       </c>
       <c r="V4" t="n">
-        <v>1.2875</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0.8295</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0.4579</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>K. GREELEY</t>
+          <t>G. PEREZ RAMIREZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>5.1695</v>
+        <v>4.878</v>
       </c>
       <c r="E5" t="n">
-        <v>2.3114</v>
+        <v>4.5389</v>
       </c>
       <c r="F5" t="n">
-        <v>2.8581</v>
+        <v>0.339</v>
       </c>
       <c r="G5" t="n">
-        <v>5.8064</v>
+        <v>3.3945</v>
       </c>
       <c r="H5" t="n">
-        <v>1.2886</v>
+        <v>-1.1095</v>
       </c>
       <c r="I5" t="n">
-        <v>4.5179</v>
+        <v>4.5041</v>
       </c>
       <c r="J5" t="n">
-        <v>4.582</v>
+        <v>4.3725</v>
       </c>
       <c r="K5" t="n">
-        <v>1.2274</v>
+        <v>0.3343</v>
       </c>
       <c r="L5" t="n">
-        <v>3.3546</v>
+        <v>4.0382</v>
       </c>
       <c r="M5" t="n">
-        <v>1.2245</v>
+        <v>-0.978</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0612</v>
+        <v>-1.4439</v>
       </c>
       <c r="O5" t="n">
-        <v>1.1633</v>
+        <v>0.4659</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.4107</v>
+        <v>1.8481</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.0534</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.6427</v>
+        <v>1.8481</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2262</v>
+        <v>0.2247</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2171</v>
+        <v>-0.0738</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0091</v>
+        <v>0.2985</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-0.5893</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.2402</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.8295</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>G. PEREZ RAMIREZ</t>
+          <t>M. MONTILLA DIAZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>4.5502</v>
+        <v>4.245</v>
       </c>
       <c r="E6" t="n">
-        <v>4.3297</v>
+        <v>2.1802</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2204</v>
+        <v>2.0649</v>
       </c>
       <c r="G6" t="n">
-        <v>3.3945</v>
+        <v>1.9714</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.1095</v>
+        <v>2.1477</v>
       </c>
       <c r="I6" t="n">
-        <v>4.5041</v>
+        <v>-0.1763</v>
       </c>
       <c r="J6" t="n">
-        <v>4.3725</v>
+        <v>2.1102</v>
       </c>
       <c r="K6" t="n">
-        <v>0.3343</v>
+        <v>2.7286</v>
       </c>
       <c r="L6" t="n">
-        <v>4.0382</v>
+        <v>-0.6183999999999999</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.978</v>
+        <v>-0.1388</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.4439</v>
+        <v>-0.581</v>
       </c>
       <c r="O6" t="n">
-        <v>0.4659</v>
+        <v>0.4422</v>
       </c>
       <c r="P6" t="n">
-        <v>1.8481</v>
+        <v>0.8214</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-1.0267</v>
       </c>
       <c r="R6" t="n">
         <v>1.8481</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1031</v>
+        <v>0.8629</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.283</v>
+        <v>0.5074</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1799</v>
+        <v>0.3556</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.5893</v>
+        <v>0.5893</v>
       </c>
       <c r="W6" t="n">
-        <v>0.2402</v>
+        <v>0.5893</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.8295</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.9861</v>
+        <v>2.9146</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.2526</v>
+        <v>0.0612</v>
       </c>
       <c r="F7" t="n">
-        <v>3.2388</v>
+        <v>2.8534</v>
       </c>
       <c r="G7" t="n">
         <v>2.1589</v>
@@ -1000,13 +1000,13 @@
         <v>2.2588</v>
       </c>
       <c r="S7" t="n">
-        <v>0.5336</v>
+        <v>0.462</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.5542</v>
+        <v>-0.2404</v>
       </c>
       <c r="U7" t="n">
-        <v>1.0878</v>
+        <v>0.7024</v>
       </c>
       <c r="V7" t="n">
         <v>-0.9384</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>2.2769</v>
+        <v>2.7751</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.6083</v>
+        <v>-0.2286</v>
       </c>
       <c r="F8" t="n">
-        <v>2.8851</v>
+        <v>3.0037</v>
       </c>
       <c r="G8" t="n">
         <v>0.6868</v>
@@ -1078,13 +1078,13 @@
         <v>1.2321</v>
       </c>
       <c r="S8" t="n">
-        <v>0.358</v>
+        <v>0.8562</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0272</v>
+        <v>0.3524</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3852</v>
+        <v>0.5038</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.4891</v>
+        <v>2.003</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0141</v>
+        <v>0.4984</v>
       </c>
       <c r="F9" t="n">
-        <v>1.475</v>
+        <v>1.5046</v>
       </c>
       <c r="G9" t="n">
         <v>2.474</v>
@@ -1156,13 +1156,13 @@
         <v>2.0534</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2437</v>
+        <v>0.2702</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2907</v>
+        <v>0.1936</v>
       </c>
       <c r="U9" t="n">
-        <v>0.047</v>
+        <v>0.0766</v>
       </c>
       <c r="V9" t="n">
         <v>-1.7679</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.6425999999999999</v>
+        <v>-0.5833</v>
       </c>
       <c r="E10" t="n">
         <v>-0.9219000000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2793</v>
+        <v>0.3386</v>
       </c>
       <c r="G10" t="n">
         <v>-0.8293</v>
@@ -1234,13 +1234,13 @@
         <v>0.4107</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.224</v>
+        <v>-0.1647</v>
       </c>
       <c r="T10" t="n">
         <v>-0.2635</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0395</v>
+        <v>0.0988</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. BITJAA KODY</t>
+          <t>J. SOLER CIRUJEDA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,40 +1267,40 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.1396</v>
+        <v>-1.2583</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.713</v>
+        <v>-4.171</v>
       </c>
       <c r="F11" t="n">
-        <v>1.5734</v>
+        <v>2.9126</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.1389</v>
+        <v>-1.8763</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.5151</v>
+        <v>-0.2659</v>
       </c>
       <c r="I11" t="n">
-        <v>0.3763</v>
+        <v>-1.6104</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.9686</v>
+        <v>-3.074</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.6</v>
+        <v>-1.0214</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.3686</v>
+        <v>-2.0526</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.1702</v>
+        <v>1.1977</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.9151</v>
+        <v>0.7554999999999999</v>
       </c>
       <c r="O11" t="n">
-        <v>0.7449</v>
+        <v>0.4422</v>
       </c>
       <c r="P11" t="n">
         <v>0.2053</v>
@@ -1312,28 +1312,28 @@
         <v>1.2321</v>
       </c>
       <c r="S11" t="n">
-        <v>0.7323</v>
+        <v>0.1724</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.0195</v>
+        <v>0.0386</v>
       </c>
       <c r="U11" t="n">
-        <v>0.7518</v>
+        <v>0.1338</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.9384</v>
+        <v>0.2402</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.6982</v>
+        <v>-0.1088</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.2402</v>
+        <v>0.3491</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>J. SOLER CIRUJEDA</t>
+          <t>J. BITJAA KODY</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,40 +1345,40 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.4362</v>
+        <v>-1.3701</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.171</v>
+        <v>-2.6471</v>
       </c>
       <c r="F12" t="n">
-        <v>2.7348</v>
+        <v>1.277</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.8763</v>
+        <v>-1.1389</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.2659</v>
+        <v>-1.5151</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.6104</v>
+        <v>0.3763</v>
       </c>
       <c r="J12" t="n">
-        <v>-3.074</v>
+        <v>-0.9686</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.0214</v>
+        <v>-0.6</v>
       </c>
       <c r="L12" t="n">
-        <v>-2.0526</v>
+        <v>-0.3686</v>
       </c>
       <c r="M12" t="n">
-        <v>1.1977</v>
+        <v>-0.1702</v>
       </c>
       <c r="N12" t="n">
-        <v>0.7554999999999999</v>
+        <v>-0.9151</v>
       </c>
       <c r="O12" t="n">
-        <v>0.4422</v>
+        <v>0.7449</v>
       </c>
       <c r="P12" t="n">
         <v>0.2053</v>
@@ -1390,22 +1390,22 @@
         <v>1.2321</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.0054</v>
+        <v>0.5018</v>
       </c>
       <c r="T12" t="n">
-        <v>0.0386</v>
+        <v>0.0464</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0441</v>
+        <v>0.4554</v>
       </c>
       <c r="V12" t="n">
-        <v>0.2402</v>
+        <v>-0.9384</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.1088</v>
+        <v>-0.6982</v>
       </c>
       <c r="X12" t="n">
-        <v>0.3491</v>
+        <v>-0.2402</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.6403</v>
+        <v>-2.4764</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.646</v>
+        <v>-2.5414</v>
       </c>
       <c r="F13" t="n">
-        <v>0.0057</v>
+        <v>0.065</v>
       </c>
       <c r="G13" t="n">
         <v>-1.6608</v>
@@ -1468,13 +1468,13 @@
         <v>0.4107</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.3634</v>
+        <v>-0.1995</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.2635</v>
+        <v>-0.1589</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.0999</v>
+        <v>-0.0407</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,19 +1501,19 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>28.5002</v>
+        <v>28.9343</v>
       </c>
       <c r="E14" t="n">
-        <v>5.136199999999999</v>
+        <v>5.570299999999998</v>
       </c>
       <c r="F14" t="n">
-        <v>23.3639</v>
+        <v>23.3638</v>
       </c>
       <c r="G14" t="n">
         <v>19.2847</v>
       </c>
       <c r="H14" t="n">
-        <v>1.5254</v>
+        <v>1.525399999999999</v>
       </c>
       <c r="I14" t="n">
         <v>17.75960000000001</v>
@@ -1522,7 +1522,7 @@
         <v>13.5806</v>
       </c>
       <c r="K14" t="n">
-        <v>3.848100000000001</v>
+        <v>3.8481</v>
       </c>
       <c r="L14" t="n">
         <v>9.732399999999998</v>
@@ -1534,7 +1534,7 @@
         <v>-2.3231</v>
       </c>
       <c r="O14" t="n">
-        <v>8.0273</v>
+        <v>8.027299999999999</v>
       </c>
       <c r="P14" t="n">
         <v>8.213800000000001</v>
@@ -1546,10 +1546,10 @@
         <v>17.4543</v>
       </c>
       <c r="S14" t="n">
-        <v>3.1189</v>
+        <v>3.5527</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.7765000000000002</v>
+        <v>-0.3426000000000001</v>
       </c>
       <c r="U14" t="n">
         <v>3.8953</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5207</v>
+        <v>1.7345</v>
       </c>
       <c r="E15" t="n">
-        <v>3.7668</v>
+        <v>2.93</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.2461</v>
+        <v>-1.1956</v>
       </c>
       <c r="G15" t="n">
         <v>0.596</v>
@@ -1624,13 +1624,13 @@
         <v>1.2321</v>
       </c>
       <c r="S15" t="n">
-        <v>1.3354</v>
+        <v>0.5491</v>
       </c>
       <c r="T15" t="n">
-        <v>0.9141</v>
+        <v>0.07729999999999999</v>
       </c>
       <c r="U15" t="n">
-        <v>0.4213</v>
+        <v>0.4719</v>
       </c>
       <c r="V15" t="n">
         <v>0.5893</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.5039</v>
+        <v>1.4926</v>
       </c>
       <c r="E16" t="n">
-        <v>1.4588</v>
+        <v>1.0404</v>
       </c>
       <c r="F16" t="n">
-        <v>1.0451</v>
+        <v>0.4522</v>
       </c>
       <c r="G16" t="n">
         <v>1.415</v>
@@ -1702,13 +1702,13 @@
         <v>0.4107</v>
       </c>
       <c r="S16" t="n">
-        <v>0.4379</v>
+        <v>-0.5733</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.0272</v>
+        <v>-0.4457</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4652</v>
+        <v>-0.1277</v>
       </c>
       <c r="V16" t="n">
         <v>0.2402</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.5412</v>
+        <v>0.1127</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.7496</v>
+        <v>-0.5404</v>
       </c>
       <c r="F17" t="n">
-        <v>0.2084</v>
+        <v>0.6531</v>
       </c>
       <c r="G17" t="n">
         <v>-0.4706</v>
@@ -1780,13 +1780,13 @@
         <v>0.8214</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.9125</v>
+        <v>-0.2586</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.8563</v>
+        <v>-0.6471</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0561</v>
+        <v>0.3885</v>
       </c>
       <c r="V17" t="n">
         <v>1.0472</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>H. KABASELE KASONGA</t>
+          <t>R. TIMONER GIMENEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.6908</v>
+        <v>-0.7814</v>
       </c>
       <c r="E18" t="n">
-        <v>1.8426</v>
+        <v>0.2312</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.5334</v>
+        <v>-1.0126</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.9395</v>
+        <v>-1.2439</v>
       </c>
       <c r="H18" t="n">
-        <v>1.6255</v>
+        <v>-1.3887</v>
       </c>
       <c r="I18" t="n">
-        <v>-3.565</v>
+        <v>0.1448</v>
       </c>
       <c r="J18" t="n">
-        <v>1.3934</v>
+        <v>-0.3739</v>
       </c>
       <c r="K18" t="n">
-        <v>1.3145</v>
+        <v>-0.308</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0789</v>
+        <v>-0.0659</v>
       </c>
       <c r="M18" t="n">
-        <v>-3.3328</v>
+        <v>-0.8699</v>
       </c>
       <c r="N18" t="n">
-        <v>0.311</v>
+        <v>-1.0807</v>
       </c>
       <c r="O18" t="n">
-        <v>-3.6439</v>
+        <v>0.2107</v>
       </c>
       <c r="P18" t="n">
-        <v>0.8214</v>
+        <v>0.616</v>
       </c>
       <c r="Q18" t="n">
         <v>-0.2053</v>
       </c>
       <c r="R18" t="n">
-        <v>1.0267</v>
+        <v>0.8214</v>
       </c>
       <c r="S18" t="n">
-        <v>0.7764</v>
+        <v>-0.9831</v>
       </c>
       <c r="T18" t="n">
-        <v>0.4144</v>
+        <v>-0.6084000000000001</v>
       </c>
       <c r="U18" t="n">
-        <v>0.362</v>
+        <v>-0.3747</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.3491</v>
+        <v>0.8295</v>
       </c>
       <c r="W18" t="n">
-        <v>0.2402</v>
+        <v>1.4189</v>
       </c>
       <c r="X18" t="n">
         <v>-0.5893</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>G. MILADINOVIC</t>
+          <t>H. KABASELE KASONGA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.1421</v>
+        <v>-1.1476</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.6826</v>
+        <v>1.4242</v>
       </c>
       <c r="F19" t="n">
-        <v>0.5405</v>
+        <v>-2.5718</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.5757</v>
+        <v>-1.9395</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.36</v>
+        <v>1.6255</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.2157</v>
+        <v>-3.565</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.8262</v>
+        <v>1.3934</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.1684</v>
+        <v>1.3145</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.6579</v>
+        <v>0.0789</v>
       </c>
       <c r="M19" t="n">
-        <v>0.2505</v>
+        <v>-3.3328</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.1917</v>
+        <v>0.311</v>
       </c>
       <c r="O19" t="n">
-        <v>0.4422</v>
+        <v>-3.6439</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.616</v>
+        <v>0.8214</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.0267</v>
+        <v>-0.2053</v>
       </c>
       <c r="R19" t="n">
-        <v>0.4107</v>
+        <v>1.0267</v>
       </c>
       <c r="S19" t="n">
-        <v>0.639</v>
+        <v>0.3196</v>
       </c>
       <c r="T19" t="n">
-        <v>0.1704</v>
+        <v>-0.0041</v>
       </c>
       <c r="U19" t="n">
-        <v>0.4686</v>
+        <v>0.3237</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.5893</v>
+        <v>-0.3491</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.2402</v>
       </c>
       <c r="X19" t="n">
         <v>-0.5893</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>R. TIMONER GIMENEZ</t>
+          <t>G. MILADINOVIC</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,64 +1969,64 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.3027</v>
+        <v>-1.782</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.08260000000000001</v>
+        <v>-1.9964</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.2201</v>
+        <v>0.2144</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.2439</v>
+        <v>-0.5757</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.3887</v>
+        <v>-0.36</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1448</v>
+        <v>-0.2157</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.3739</v>
+        <v>-0.8262</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.308</v>
+        <v>-0.1684</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.0659</v>
+        <v>-0.6579</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.8699</v>
+        <v>0.2505</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.0807</v>
+        <v>-0.1917</v>
       </c>
       <c r="O20" t="n">
-        <v>0.2107</v>
+        <v>0.4422</v>
       </c>
       <c r="P20" t="n">
-        <v>0.616</v>
+        <v>-0.616</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.2053</v>
+        <v>-1.0267</v>
       </c>
       <c r="R20" t="n">
-        <v>0.8214</v>
+        <v>0.4107</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.5044</v>
+        <v>-0.0009</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.9222</v>
+        <v>-0.1434</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.5822000000000001</v>
+        <v>0.1425</v>
       </c>
       <c r="V20" t="n">
-        <v>0.8295</v>
+        <v>-0.5893</v>
       </c>
       <c r="W20" t="n">
-        <v>1.4189</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
         <v>-0.5893</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.608</v>
+        <v>-2.337</v>
       </c>
       <c r="E21" t="n">
-        <v>-4.93</v>
+        <v>-4.3024</v>
       </c>
       <c r="F21" t="n">
-        <v>1.322</v>
+        <v>1.9654</v>
       </c>
       <c r="G21" t="n">
         <v>-1.2365</v>
@@ -2092,13 +2092,13 @@
         <v>0.616</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.086</v>
+        <v>0.185</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.651</v>
+        <v>-0.0234</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.435</v>
+        <v>0.2084</v>
       </c>
       <c r="V21" t="n">
         <v>1.1786</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.3422</v>
+        <v>-4.5218</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.9775</v>
+        <v>-4.1867</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.3648</v>
+        <v>-0.3351</v>
       </c>
       <c r="G22" t="n">
         <v>-2.108</v>
@@ -2170,13 +2170,13 @@
         <v>0.8214</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.1274</v>
+        <v>-0.307</v>
       </c>
       <c r="T22" t="n">
-        <v>0.1045</v>
+        <v>-0.1047</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2319</v>
+        <v>-0.2023</v>
       </c>
       <c r="V22" t="n">
         <v>1.1786</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.7137</v>
+        <v>-5.4975</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.9651</v>
+        <v>-5.6513</v>
       </c>
       <c r="F23" t="n">
-        <v>0.2514</v>
+        <v>0.1537</v>
       </c>
       <c r="G23" t="n">
         <v>-4.1799</v>
@@ -2248,13 +2248,13 @@
         <v>1.0267</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.7392</v>
+        <v>-0.523</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.7441</v>
+        <v>-0.4303</v>
       </c>
       <c r="U23" t="n">
-        <v>0.005</v>
+        <v>-0.0927</v>
       </c>
       <c r="V23" t="n">
         <v>-0.5893</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-7.208</v>
+        <v>-6.4409</v>
       </c>
       <c r="E24" t="n">
-        <v>-5.9549</v>
+        <v>-5.3273</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.2531</v>
+        <v>-1.1137</v>
       </c>
       <c r="G24" t="n">
         <v>-2.8842</v>
@@ -2326,13 +2326,13 @@
         <v>1.2321</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.9686</v>
+        <v>-0.2015</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.3097</v>
+        <v>-0.6821</v>
       </c>
       <c r="U24" t="n">
-        <v>0.3411</v>
+        <v>0.4806</v>
       </c>
       <c r="V24" t="n">
         <v>-0.4805</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-8.9762</v>
+        <v>-8.634399999999999</v>
       </c>
       <c r="E25" t="n">
-        <v>-7.0899</v>
+        <v>-6.9853</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.8862</v>
+        <v>-1.6491</v>
       </c>
       <c r="G25" t="n">
         <v>-6.6576</v>
@@ -2404,13 +2404,13 @@
         <v>0.8214</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.9695</v>
+        <v>-0.6277</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.9881</v>
+        <v>-0.8835</v>
       </c>
       <c r="U25" t="n">
-        <v>0.0186</v>
+        <v>0.2558</v>
       </c>
       <c r="V25" t="n">
         <v>-0.9384</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-28.5003</v>
+        <v>-27.8028</v>
       </c>
       <c r="E26" t="n">
         <v>-23.364</v>
       </c>
       <c r="F26" t="n">
-        <v>-5.1363</v>
+        <v>-4.4391</v>
       </c>
       <c r="G26" t="n">
         <v>-19.2849</v>
@@ -2470,7 +2470,7 @@
         <v>-3.8482</v>
       </c>
       <c r="O26" t="n">
-        <v>-9.732500000000002</v>
+        <v>-9.732499999999998</v>
       </c>
       <c r="P26" t="n">
         <v>-8.213600000000001</v>
@@ -2482,13 +2482,13 @@
         <v>9.240600000000001</v>
       </c>
       <c r="S26" t="n">
-        <v>-3.1189</v>
+        <v>-2.4214</v>
       </c>
       <c r="T26" t="n">
-        <v>-3.8952</v>
+        <v>-3.8954</v>
       </c>
       <c r="U26" t="n">
-        <v>0.7766</v>
+        <v>1.474</v>
       </c>
       <c r="V26" t="n">
         <v>2.1168</v>
